--- a/02_加值成品/九上/九上6-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上6-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上6-3 地層、化石與地質年代　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三上學期 九上6-3 地層、化石與地質年代　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>沉積物層層堆積形成？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>地質歷史</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>時間</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>環境與年代</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>地層</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>岩層</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>未受擾動地層越下層越？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>老</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>沉積岩</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>時間</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>地層</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>疊置</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>古生物遺骸或遺跡是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>老</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>時間</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>指準化石</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>化石</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>保存</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>化石多保存在哪類岩石？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>沉積岩</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>地質歷史</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>地層</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>化石</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>層理</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>可用來對比地層年代的化石是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>下老上新</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>指準化石</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>環境與年代</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>古植物</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>定年</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>地層記錄了什麼順序？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>新</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>老</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>時間</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>地質年代</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>歷史</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>科學家用地層化石重建？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>地質年代</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>沉積岩</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>化石</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>下老上新</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>歷史</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>越上層的地層通常越？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>沉積岩</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>環境與年代</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>新</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>古植物</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>疊置</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>地層中通常越下層形成時間越？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>老</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>沉積岩</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>早(老)</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>地質歷史</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>疊置</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>化石多保存在哪一類岩石？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>指準化石</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>沉積岩</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>地殼變動</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>地質年代</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>沉積</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上6-3 地層、化石與地質年代　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三上學期 九上6-3 地層、化石與地質年代　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>疊置原理指未擾動時？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>老</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>古植物</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>時間</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>下老上新</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>順序</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>好的指準化石特徵？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>分布廣存在時間短</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>需先判斷是否擾動再解讀</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>該地曾為海洋後經抬升</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>以化石對比、地層順序排年代</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>定年佳</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>化石能指示當時的？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>新</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>層理</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>環境與年代</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>時間</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>線索</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>煤是什麼古生物沉積形成？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>下老上新</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>老</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>沉積岩</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>古植物</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>沉積</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>地層若傾斜倒轉可能因？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>層理</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>沉積岩</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>化石</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>地殼變動</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>擾動</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>化石形成需要什麼條件？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>快速掩埋等特定條件</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>分布廣存在時間短</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>以化石對比、地層順序排年代</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>該地曾為海洋後經抬升</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>稀有</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>地層剖面能幫助了解？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>環境與年代</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>早(老)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>地質歷史</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>指準化石</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>紀錄</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>海生化石出現在山上說明？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>該地曾為海洋後經抬升</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>快速掩埋等特定條件</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>曾在海洋後抬升</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>曾是海洋後抬升</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>變動</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>對比不同地區地層年代的化石稱？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>新</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>沉積岩</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>老</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>指準化石</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>定年</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>地層一層層堆疊的排列稱？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>老</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>新</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>層理</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>沉積岩</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>層理</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上6-3 地層、化石與地質年代　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三上學期 九上6-3 地層、化石與地質年代　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>如何用疊置原理判斷地層先後？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>未擾動時下層先沉積較老</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>快速掩埋等特定條件</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>該地曾為海洋後經抬升</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>分布廣存在時間短</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>原理</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何指準化石要分布廣且存在時間短？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>曾在海洋後抬升</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>快速掩埋等特定條件</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>遺骸多被分解需特殊掩埋保存</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>廣可跨區對比、短代表特定年代</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>定年</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>高山發現海洋生物化石代表什麼？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>該地曾為海洋後經抬升</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>由生物種類推當時氣候環境</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>以化石對比、地層順序排年代</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>需先判斷是否擾動再解讀</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>地殼變動</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>分析化石如何重建古環境？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>快速掩埋等特定條件</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>未擾動時下層先沉積較老</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>由生物種類推當時氣候環境</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>遺骸多被分解需特殊掩埋保存</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>推論</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>地層倒轉時疊置原理還適用嗎？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>曾在海洋後抬升</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>由生物種類推當時氣候環境</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>需先判斷是否擾動再解讀</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>分布廣存在時間短</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>限制</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>煤層的存在說明古代該地？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>有繁茂植物與沉積環境</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>遺骸多被分解需特殊掩埋保存</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>以化石對比、地層順序排年代</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>由生物種類推當時氣候環境</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>古環境</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>化石與地層如何共同建立地質年代？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>快速掩埋等特定條件</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>以化石對比、地層順序排年代</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>遺骸多被分解需特殊掩埋保存</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>未擾動時下層先沉積較老</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>綜合</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>為何多數生物難以形成化石？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>由生物種類推當時氣候環境</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>曾是海洋後抬升</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>遺骸多被分解需特殊掩埋保存</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>分布廣存在時間短</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>高山發現貝殼化石可推論該地？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>遺骸多被分解需特殊掩埋保存</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>廣可跨區對比、短代表特定年代</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>曾在海洋後抬升</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>曾是海洋後抬升</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>地殼變動</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>為何多數生物不易形成化石？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>遺骸多被分解需特殊掩埋保存</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>遺骸多被分解需特殊掩埋</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>該地曾為海洋後經抬升</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>需先判斷是否擾動再解讀</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九上/九上6-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上6-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>岩層</t>
+          <t>岩層：碎屑物質一層層在水底或陸地上堆積壓密膠結，就形成了層狀排列的地層</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>疊置</t>
+          <t>疊置：根據地層疊置原理，若地層沒有被翻轉過，越下面的地層是越早形成的，也就是越老</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>保存</t>
+          <t>保存：古代生物的遺體、遺骸或活動痕跡，在特定條件下被保存下來的證據，稱為化石</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>層理</t>
+          <t>層理：生物遺骸容易隨著沉積物一層層被掩埋保存下來，所以化石大多發現在沉積岩中</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>定年</t>
+          <t>定年：某些生存時間短、分布範圍廣的生物化石，可以用來對比不同地區地層是否形成於同一時代，這種化石叫指準化石</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>歷史</t>
+          <t>歷史：地層一層一層依序堆積，如實記錄了地球歷史上不同時期發生的事件先後順序</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>歷史</t>
+          <t>歷史：科學家透過分析地層的排列順序和其中含有的化石種類，可以重建出地球過去各時期的地質年代與歷史</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>疊置</t>
+          <t>疊置：根據地層疊置原理，未受擾動的地層越往上層形成的時間越晚，也就是越新</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>疊置</t>
+          <t>疊置：根據地層疊置原理,若地層沒有被翻轉過,越下面的地層是越早形成的,也就是越老</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>沉積</t>
+          <t>沉積：生物遺骸容易隨著沉積物一層層被掩埋保存下來,所以化石大多發現在沉積岩中</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>順序</t>
+          <t>順序：地層疊置原理指出，在沒有受到擾動翻轉的情況下，地層是由下往上依序堆積形成的，所以下層較老、上層較新</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>定年佳</t>
+          <t>定年佳：理想的指準化石要分布範圍廣，才能用來對比不同地區的地層；同時該生物存在的時間要短，才能精準指出特定的年代</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>線索</t>
+          <t>線索：化石中生物的種類能透露出當時的生存環境(如海洋、陸地、氣候)，也能幫助推斷該地層形成的大約年代</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>沉積</t>
+          <t>沉積：煤是古代大量植物遺體被掩埋，經過長時間的壓密和化學變化後形成的沉積物</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>擾動</t>
+          <t>擾動：原本水平堆積的地層，可能因為地殼受力擠壓、褶皺甚至翻轉，變成傾斜或倒轉的狀態，這種現象稱為地層受到擾動</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>稀有：生物死後遺骸通常會被分解或啃食，只有在被迅速掩埋、隔絕空氣等特定條件下才有機會保存下來形成化石，所以化石其實相當稀少珍貴</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>紀錄</t>
+          <t>紀錄：從地層剖面(垂直切面)可以觀察到不同時期堆積的地層順序與特徵，幫助了解該地區的地質歷史</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>變動</t>
+          <t>變動：海洋生物的化石按理應該只出現在海底沉積的地層中，若在高山地層發現，代表這塊地層原本是在海底形成，後來因為地殼隆起抬升才變成現在的高山</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>定年</t>
+          <t>定年：某些生存時間短、分布範圍廣的生物化石,可以用來對比不同地區地層是否形成於同一時代,這種化石叫指準化石</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>層理</t>
+          <t>層理：沉積物一層一層堆積形成的紋理構造,稱為層理,是沉積岩常見的特徵</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>原理</t>
+          <t>原理：只要能確認地層沒有經過翻轉等擾動，就可以直接依照疊置原理判斷：位置越下面的地層是越早堆積形成的，也就是年代越老</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>定年</t>
+          <t>定年：分布範圍廣的化石才能在不同地區的地層中都找到，用來互相對比是否屬於同一時期；生存時間短則代表這種生物只存在於地質歷史上很短暫的一段時間，找到它就能精準鎖定該地層形成的年代範圍</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>地殼變動</t>
+          <t>地殼變動：海洋生物只可能在海底環境中死亡沉積形成化石，若在高山地層中發現，代表這塊地層原本是在海底形成的沉積岩，後來因為地殼劇烈隆起抬升，才變成現在的高山地形</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>推論</t>
+          <t>推論：透過辨識化石中生物的種類(例如珊瑚代表溫暖淺海、蕨類代表溫暖潮濕)，可以推論出該地層形成時當地的氣候與生態環境</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>限制</t>
+          <t>限制：疊置原理只適用於未受擾動的地層；如果地層曾經受地殼變動而傾斜、褶皺甚至上下翻轉，必須先透過其他證據(如沉積構造)判斷地層是否被翻轉過，才能正確解讀先後順序，不能直接套用疊置原理</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>古環境</t>
+          <t>古環境：煤是由大量古代植物遺體長期堆積並經沉積作用形成的，因此某地層中有煤層存在，可以推論當地古代曾有茂密的植物生長，且屬於適合沉積掩埋的環境(如沼澤)</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>綜合</t>
+          <t>綜合：利用指準化石可以對比不同地區的地層是否形成於相同時代，再結合疊置原理判斷同一地區地層的先後順序，兩者互相搭配，科學家就能建立起完整的地質年代架構</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>稀有：生物死亡後遺骸大多會被微生物分解或遭其他動物啃食，只有在被迅速掩埋、隔絕空氣等特殊條件下才有機會完整保存下來形成化石，所以能形成化石的生物其實非常稀少</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>地殼變動</t>
+          <t>地殼變動：貝殼是海洋生物,若在高山地層中發現貝殼化石,可以推論這塊地層原本是在海底形成,後來因為地殼隆起抬升才變成現在的高山</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>稀有：生物死亡後遺骸通常會被微生物分解或遭啃食,只有在被迅速掩埋、隔絕空氣等特殊條件下才有機會保存成化石,所以化石其實很稀少</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九上/九上6-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上6-3_三種難度測驗卷.xlsx
@@ -608,17 +608,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>沉積岩</t>
+          <t>地層</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>時間</t>
+          <t>化石</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>地層</t>
+          <t>新</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -643,17 +643,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
+          <t>層理</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
           <t>老</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>時間</t>
-        </is>
-      </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>指準化石</t>
+          <t>地質年代</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>下老上新</t>
+          <t>環境與年代</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -733,12 +733,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>環境與年代</t>
+          <t>古植物</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>古植物</t>
+          <t>沉積岩</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>沉積岩</t>
+          <t>環境與年代</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>環境與年代</t>
+          <t>地層</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>古植物</t>
+          <t>指準化石</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -883,22 +883,22 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>老</t>
+          <t>地層</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>時間</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>早(老)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
           <t>沉積岩</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>早(老)</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>地質歷史</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>老</t>
+          <t>環境與年代</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>古植物</t>
+          <t>時間</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>時間</t>
+          <t>地層</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -1359,17 +1359,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>新</t>
+          <t>老</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>地層</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
           <t>沉積岩</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>老</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1795,14 +1795,14 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
+          <t>曾是海洋後抬升</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
           <t>由生物種類推當時氣候環境</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>曾是海洋後抬升</t>
-        </is>
-      </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
           <t>遺骸多被分解需特殊掩埋保存</t>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>分布廣存在時間短</t>
+          <t>未擾動時下層先沉積較老</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>遺骸多被分解需特殊掩埋保存</t>
+          <t>快速掩埋等特定條件</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>該地曾為海洋後經抬升</t>
+          <t>由生物種類推當時氣候環境</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>需先判斷是否擾動再解讀</t>
+          <t>曾在海洋後抬升</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
